--- a/www/download/COUNTRY.SVK.WIOD16.xlsx
+++ b/www/download/COUNTRY.SVK.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Eslováquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.52911740096737</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.60319119312196</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1.50368167644417</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.21434606376573</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1.06897622569735</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1.03148528984672</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.984085316768746</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.81761183527841</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.705818071274427</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.717064070002902</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.75432451679925</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.719139530176793</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.778338085527401</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.752965474987109</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.752718194502933</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.013</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.036</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.061</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.058</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.085</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.131</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.176</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.248</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.203</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.208</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.192</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.223</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.812</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.827</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.823</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.785</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.799</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.861</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.901</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.838</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.809</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.864</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.855</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.896</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3497.542</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3501.492</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3406.647</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3335.265</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3412.14</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3529.301</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3606.48</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3699.132</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3837.944</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3720.763</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3733.664</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3771.814</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3765.412</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3701.243</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3732.752</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3149.145</t>
+          <t>4608195569.77742</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3147.712</t>
+          <t>4603822530.17359</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3048.128</t>
+          <t>4548724011.00306</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2953.589</t>
+          <t>4633847714.48055</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2958.433</t>
+          <t>4710682177.81283</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3040.162</t>
+          <t>4812121262.19187</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3098.051</t>
+          <t>5274597526.21944</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3160.638</t>
+          <t>5581776089.41722</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3235.005</t>
+          <t>5707699878.60704</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3093.644</t>
+          <t>5659299402.86449</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3100.7</t>
+          <t>5349044006.69889</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3160.662</t>
+          <t>5915728927.85524</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3171.324</t>
+          <t>5752561751.29652</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3127.058</t>
+          <t>5847899146.89606</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3177.435</t>
+          <t>5944496703.15979</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>887354532.880413</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>845687677.410025</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>861284145.749882</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>899555715.438676</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1090320068.45285</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1149255817.6423</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1268869758.46601</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1512532355.7828</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1446095436.42002</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1593207686.35224</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1371067424.10509</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1428681505.82526</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1531168288.08007</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1608565811.00264</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1640018888.47212</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5570643.53038642</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5218712.85694044</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4408681.80277529</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3234688.97135604</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2701492.82334872</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2486296.29387626</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2215149.81400623</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1717521.82382103</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1395760.6139131</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1633748.62791045</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1529117.8385233</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1438744.3973831</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1471149.10188441</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1413317.72991126</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1361713.20277476</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>17022.7379318303</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16807.1416153691</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16067.5858054835</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>16993.777100728</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19058.6894207715</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>20493.473179461</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>21669.44994424</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>24703.8904354529</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>27938.9880150613</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23659.876453391</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>26393.6866517765</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>28151.3554698297</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>26902.9478792738</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>26476.4930973279</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>26825.4500467708</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>37443.2763667251</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>37056.1385598626</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>36832.4002275355</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>40834.7157054659</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>45894.5966362946</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>50337.1032393548</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>58288.6063612809</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>69644.3514997283</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>77297.32720357</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>69746.7619741055</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>73035.0001285121</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>85777.614346037</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>81272.1972870936</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>82537.0051052019</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>84289.0359169522</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.54891408485587</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.72207386258728</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.5390503993849</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.28338639765037</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.71336196186683</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.64533096402932</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.44158313280738</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.0896333145642</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.23706189683347</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.941770697254866</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.26152262498969</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.21229293380843</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.07117925879755</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.94400376945154</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.937438051680105</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10825.5872075986</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11997.3344172002</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>13675.2298022419</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>17797.0562294426</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>20787.6766409607</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>23140.1873976793</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>24586.3924799378</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>31206.1377601449</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>37172.2329199294</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>36486.747950416</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>35296.4511982166</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>40388.1841585647</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>37120.2747053774</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>40960.3513101226</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>42856.9990720959</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.52911740096737</t>
+          <t>489.701899461054</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.60319119312196</t>
+          <t>462.756595026006</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.50368167644417</t>
+          <t>472.573521431564</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.21434606376573</t>
+          <t>492.653491044983</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.06897622569735</t>
+          <t>610.864634290736</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.03148528984672</t>
+          <t>638.702548485181</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.984085316768746</t>
+          <t>692.164892054841</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.81761183527841</t>
+          <t>812.617111487499</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.705818071274427</t>
+          <t>760.862588877209</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717064070002902</t>
+          <t>866.995182002938</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75432451679925</t>
+          <t>758.027690205332</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.719139530176793</t>
+          <t>770.486073056236</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778338085527401</t>
+          <t>821.336463159288</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.752965474987109</t>
+          <t>867.324377909684</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752718194502933</t>
+          <t>865.198776323434</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-250809689.189262</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-372823693.344308</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-305699282.286646</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-43104297.6174625</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>373126316.391632</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>405352875.801009</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>811804542.316084</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1504800339.09526</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1331118521.85373</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1487306054.8714</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1157084771.21641</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1188647533.89838</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1703844667.86116</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1938392200.17911</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1961422894.93662</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-191973350.253094</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-305054565.719259</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-249211818.773483</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>262658.589979026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>323690662.214702</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>294509293.731835</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>658070998.875009</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1252859253.5167</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1092036486.32635</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1254294628.90112</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1080981463.9248</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1201743981.64609</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1214981233.77459</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1243137315.72777</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1201481833.04855</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>-58836338.9361688</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-67769127.6250487</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>-56487463.5131637</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>-43366956.2074416</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>49435654.1769296</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>110843582.069174</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>153733543.441075</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>251941085.578564</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>239082035.527377</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>233011425.970273</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>76103307.2916047</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>-13096447.7477177</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>488863434.086568</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>695254884.451338</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>759941061.888062</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1737.90996837801</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1722.41422708618</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>1672.4615097611</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1617.57177125207</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1657.49686253418</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1689.57962831229</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1689.97812556254</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>1698.07178814921</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1702.09670630327</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>1683.50583907446</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1714.29677176804</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>1704.54089502012</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1701.13504698966</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1686.08185999364</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1676.26903151609</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1737.43412870295</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1719.70556352904</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1669.81874122858</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1617.89056925258</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1658.1094231167</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1692.52345089401</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>1692.44435611983</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1699.78131063336</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1707.08069107479</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1688.82237536299</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1720.70165891688</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1707.94730489107</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1704.17669818684</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1688.32286995284</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1679.0451122744</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7549.08728288994</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8669.91061516631</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10554.3584899283</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>17306.745809473</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>25155.3776517743</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>30233.7745529521</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>40161.7815336515</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>57179.0063135581</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>69205.9979557776</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>53443.3966531927</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>60410.0946290949</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>72835.90918015</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>75864.006610755</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>81174.5098892392</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>82119.4564426122</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>814199267.220809</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>911932511.029652</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>953782559.569576</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1155279008.07571</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1445033410.33939</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1599460333.48505</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1944455799.22912</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2213853461.44354</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2262852891.05789</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2110170268.35828</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2115964479.41063</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2588677759.07722</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2510182624.46424</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2564877935.22819</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2574847951.13539</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>10472.2251966503</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12606.4508639589</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14416.6135649042</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>19615.4620901537</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>27558.6608466245</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>33271.7365099865</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>42288.0002016145</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>56551.4669077138</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>68637.4071128475</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>52851.7033367813</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>59715.7367505469</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>72436.5720222484</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>69957.8670814147</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>74120.8378297995</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>74994.6773974078</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3497.542</t>
+          <t>1015017157.98318</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3501.492</t>
+          <t>1169309109.51279</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3406.647</t>
+          <t>1271743096.78007</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3335.265</t>
+          <t>1463438006.49867</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3412.14</t>
+          <t>2149800758.27601</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3529.301</t>
+          <t>2387876117.5412</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3606.48</t>
+          <t>3000279981.34967</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3699.132</t>
+          <t>3657280006.66836</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3837.944</t>
+          <t>3545020583.41937</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3720.763</t>
+          <t>3539875073.27604</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3733.664</t>
+          <t>3212999251.57656</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3771.814</t>
+          <t>3744559949.31143</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3765.412</t>
+          <t>3724236745.313</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3701.243</t>
+          <t>3915063692.59318</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3732.752</t>
+          <t>3947934614.9207</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3149.145</t>
+          <t>-2923.13791376037</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3147.712</t>
+          <t>-3936.54024879261</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3048.128</t>
+          <t>-3862.25507497587</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2953.589</t>
+          <t>-2308.71628068069</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2958.433</t>
+          <t>-2403.2831948502</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3040.162</t>
+          <t>-3037.9619570344</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3098.051</t>
+          <t>-2126.21866796292</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3160.638</t>
+          <t>627.539405844222</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3235.005</t>
+          <t>568.590842930073</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3093.644</t>
+          <t>591.693316411417</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3100.7</t>
+          <t>694.357878547988</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3160.662</t>
+          <t>399.33715790154</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3171.324</t>
+          <t>5906.13952934034</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3127.058</t>
+          <t>7053.67205943977</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3177.435</t>
+          <t>7124.77904520442</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4608.211</t>
+          <t>-200817890.762373</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4604.776</t>
+          <t>-257376598.483137</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4549.374</t>
+          <t>-317960537.21049</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4631.658</t>
+          <t>-308158998.422958</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4709.672</t>
+          <t>-704767347.936622</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>4812.199</t>
+          <t>-788415784.056149</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5274.019</t>
+          <t>-1055824182.12055</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5578.699</t>
+          <t>-1443426545.22483</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5707.804</t>
+          <t>-1282167692.36147</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5659.673</t>
+          <t>-1429704804.91776</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>5350.436</t>
+          <t>-1097034772.16593</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>5917.614</t>
+          <t>-1155882190.23422</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5752.929</t>
+          <t>-1214054120.84877</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>5847.994</t>
+          <t>-1350185757.36499</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>5944.163</t>
+          <t>-1373086663.78532</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>9718.43476954295</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>10300.071714762</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>11784.7759343294</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>15946.5230304452</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>20030.3947604643</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>21948.53661</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>26529.2554058216</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>36022.6927769905</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>45613.1266264514</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>39038.5138607752</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>39571.87986</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>43649.8444964378</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>42371.1697841789</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>43181.464764115</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>44566.9238</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2095.012</t>
+          <t>-0.0132502929135846</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2088.105</t>
+          <t>-0.0152430825864281</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1984.313</t>
+          <t>-0.0139333333938764</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1928.422</t>
+          <t>-0.00977127532594166</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1956.209</t>
+          <t>-0.00056223242040054</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1959.133</t>
+          <t>-0.00133599034361492</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1960.891</t>
+          <t>0.0111943633256575</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1979.939</t>
+          <t>0.0183238668099623</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2063.038</t>
+          <t>0.0237583718159592</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1919.778</t>
+          <t>0.0103760096321084</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1933.059</t>
+          <t>0.0155792381687646</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1941.483</t>
+          <t>0.0117909082895647</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1904.229</t>
+          <t>0.0173119863087594</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1875.908</t>
+          <t>0.0125019176961455</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1891.869</t>
+          <t>0.00856509867104256</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>8292.79040011203</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>8382.68524780722</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>9734.74574836978</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>12946.373342093</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>15582.4039699243</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>17824.937422011</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>20479.2173805289</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>27196.7966887557</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>34292.6288332079</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>33476.1571940205</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33026.7533831632</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>36265.8478538414</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>34522.5704274247</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>36412.6291403868</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>37910.1140506309</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>887.386</t>
+          <t>9261.9552159524</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>845.848</t>
+          <t>9350.782877922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>861.379</t>
+          <t>10907.7460093141</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>899.436</t>
+          <t>14588.3490031015</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1090.206</t>
+          <t>17986.6750950025</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1149.28</t>
+          <t>20641.4352968497</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1268.892</t>
+          <t>23834.9656753049</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1511.945</t>
+          <t>31921.6429686861</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1446.023</t>
+          <t>40521.8704183616</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1593.293</t>
+          <t>40019.4933228012</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1371.351</t>
+          <t>39594.7034793902</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1428.982</t>
+          <t>43233.9699830967</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1531.233</t>
+          <t>40875.669714652</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1608.591</t>
+          <t>42994.9050382179</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1639.911</t>
+          <t>44342.5362429497</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>254.88</t>
+          <t>124815.596975232</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>272.14</t>
+          <t>130105.422886244</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>253.87</t>
+          <t>149048.71543557</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>228.38</t>
+          <t>190665.861539377</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>171.36</t>
+          <t>227438.027389066</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>164.53</t>
+          <t>253107.862868188</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>144.15</t>
+          <t>277682.411273661</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>345677.632379492</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>123.72</t>
+          <t>435614.218315439</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>94.17</t>
+          <t>436511.621329372</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>126.11</t>
+          <t>418214.007566577</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>121.18</t>
+          <t>447692.025833042</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>107.11</t>
+          <t>417052.932650754</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>442940.768063548</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>93.76</t>
+          <t>456045.182311835</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.571</t>
+          <t>13570.0563318088</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.227</t>
+          <t>13666.8907411215</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.409</t>
+          <t>14172.2415298927</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.231</t>
+          <t>14423.488861808</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>14554.2784540171</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>15630.636328808</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>16846.2244818741</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>18200.2753902864</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>19424.902020407</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.634</t>
+          <t>19177.6128100027</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>19620.4486879926</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>19977.1068986924</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>20116.0416464677</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>20308.1176134594</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>20881.5474508397</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>12152.8807433925</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12254.1717698947</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>12628.4417996728</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>12754.4607988448</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>12565.9939788563</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>13461.6018421266</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>14428.4246036821</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>15488.3373782726</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>16403.6288460366</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>16051.2599587433</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>16365.913987299</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>16765.7714721239</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>16955.301695837</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>17174.8499122384</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>17861.0370590592</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9171.74398749282</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10014.126711203</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11598.4843581491</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>15934.0076010835</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>20659.8036083306</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>22802.0377369944</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>27694.8702808798</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>37540.2886550498</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>47521.717486986</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>41015.9967378568</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>41811.9068276098</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>45666.8797771315</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>44340.2893654552</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>46497.9603367205</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>46763.0710570503</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3149145000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3147712000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3048128000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2953589000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2958433000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3040162000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3098051000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3160638000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3235005000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3093644000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3100700000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3160662000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3171324000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3127058000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3177435000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3497541772.78546</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3501492497.90148</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3406647308.54267</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3335265229.60849</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3412140476.36069</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3529300675.50771</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3606480451.78643</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3699132079.45275</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3837944163.7089</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3720762792.72847</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3733664494.60078</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3771813748.64838</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3765412498.17778</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3701242694.88282</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3732752350.90171</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2095011792.09451</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2088104703.93873</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1984313074.92189</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1928422270.56475</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1956209121.92304</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1959132959.12392</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1960891402.37788</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1979939248.17767</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2063038455.15895</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1919778365.25565</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1933059370.86262</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1941483091.84005</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1904228926.16946</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1875908402.53186</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1891868825.27547</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2013050</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2036100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2040130</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2061490</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2057850</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2085230</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2130930</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2176240</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2248250</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2203170</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2169850</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2208390</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2209520</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2192260</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2223140</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1812030</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1827500</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1822540</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1825940</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1784880</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1799360</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1833190</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1861310</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1900600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1837620</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1808730</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1854260</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1864240</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1854630</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1895540</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3497541772.78546</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3501492497.90148</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3406647308.54267</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3335265229.60849</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3412140476.36069</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3529300675.50771</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3606480451.78643</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3699132079.45275</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3837944163.7089</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3720762792.72847</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3733664494.60078</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3771813748.64838</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3765412498.17778</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3701242694.88282</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3732752350.90171</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3149145000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3147712000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3048128000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2953589000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2958433000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3040162000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3098051000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3160638000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3235005000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3093644000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3100700000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3160662000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3171324000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3127058000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3177435000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>47953.6234255736</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>49500.2297137135</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>57598.1241747581</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>78315.0614172103</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>95245.6109264023</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>107333.35899</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>129506.065420792</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>174225.797122471</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>222650.928757272</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>193954.467087264</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>200018.03661</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>228356.727199755</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>218230.673529046</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>226612.921739587</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>229289.13625</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18433.8896655736</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>19364.9017937135</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22506.3408147581</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>30522.5401372103</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>38646.5438564023</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>43443.34995</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>51529.5386207924</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>69461.6249724713</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>88043.4598372719</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>81035.9224472636</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>81406.59705</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>88900.7383997552</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>85216.1004090459</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>89493.2372395871</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>91105.6073</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>206001.217552433</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>207261.622037485</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>204373.872333848</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>197047.125520092</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>191875.899717932</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>193022.961968964</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>190063.399090794</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>198169.288085811</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>204605.350775888</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>208123.660719496</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>207246.35530196</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>207064.283372338</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>203761.250932417</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>207384.480865836</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>213973.81393563</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
